--- a/audit_2026-05-21/audit_report_corrected.xlsx
+++ b/audit_2026-05-21/audit_report_corrected.xlsx
@@ -505,7 +505,7 @@
     <row r="1" ht="95" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Проверка членов СРО (исправленная методика). Компаний: 89. НОСТРОЙ проверено: 89/89; дела проверены: 89/89. Фильтр контрактов: дата окончания ≥ 01.01.2023 (цифры из выверенной выгрузки ЦИСК). НОСТРОЙ (reestr.nostroy.ru): статус права + уровень КФ ОДО (обеспечение договорных обязательств, не путать с КФ ВВ); приостановлено: 19, ОДО не установлен: 19. Суды: берутся ТОЛЬКО дела категории «…по договорам подряда», затем дата ≥ 01.01.2025. Описание = № дела + сумма иска + роль (истец/ответчик/третье лицо). Риск — Высокий: 57, Средний: 3, Низкий: 29, Ожидает: 0.</t>
+          <t>Проверка членов СРО (исправленная методика). Компаний: 89. НОСТРОЙ проверено: 89/89; дела проверены: 89/89. Фильтр контрактов: дата окончания ≥ 01.01.2023 (цифры из выверенной выгрузки ЦИСК). НОСТРОЙ (reestr.nostroy.ru): статус права + уровень КФ ОДО (обеспечение договорных обязательств, не путать с КФ ВВ); приостановлено: 23, ОДО не установлен: 16. Суды: берутся ТОЛЬКО дела категории «…по договорам подряда», затем дата ≥ 01.01.2025. Описание = № дела + сумма иска + роль (истец/ответчик/третье лицо). Риск — Высокий: 59, Средний: 3, Низкий: 27, Ожидает: 0.</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>действителен</t>
+          <t>приостановлен</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -2807,14 +2807,14 @@
       <c r="K40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="7" t="inlineStr">
-        <is>
-          <t>Низкий</t>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>Высокий</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>НОСТРОЙ действителен; дел по подряду 2025+ нет; штрафов нет</t>
+          <t>статус НОСТРОЙ приостановлен</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>действителен</t>
+          <t>приостановлен</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -3456,14 +3456,14 @@
       <c r="K51" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L51" s="7" t="inlineStr">
-        <is>
-          <t>Низкий</t>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>Высокий</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>НОСТРОЙ действителен; дел по подряду 2025+ нет; штрафов нет</t>
+          <t>статус НОСТРОЙ приостановлен</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>не установлен</t>
+          <t>Первый уровень</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>уровень ответственности (ОДО) не установлен; арбитражные дела по подряду 2025+ (1)</t>
+          <t>арбитражные дела по подряду 2025+ (1)</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>действителен</t>
+          <t>приостановлен</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -3633,14 +3633,14 @@
       <c r="K54" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L54" s="7" t="inlineStr">
-        <is>
-          <t>Низкий</t>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>Высокий</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>НОСТРОЙ действителен; дел по подряду 2025+ нет; штрафов нет</t>
+          <t>статус НОСТРОЙ приостановлен</t>
         </is>
       </c>
     </row>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>действителен</t>
+          <t>приостановлен</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -4341,14 +4341,14 @@
       <c r="K66" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L66" s="7" t="inlineStr">
-        <is>
-          <t>Низкий</t>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>Высокий</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>НОСТРОЙ действителен; дел по подряду 2025+ нет; штрафов нет</t>
+          <t>статус НОСТРОЙ приостановлен</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>не установлен</t>
+          <t>Первый уровень</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
@@ -4577,14 +4577,14 @@
       <c r="K70" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L70" s="5" t="inlineStr">
-        <is>
-          <t>Высокий</t>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t>Низкий</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>уровень ответственности (ОДО) не установлен</t>
+          <t>НОСТРОЙ действителен; дел по подряду 2025+ нет; штрафов нет</t>
         </is>
       </c>
     </row>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>не установлен</t>
+          <t>Первый уровень</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
@@ -5580,14 +5580,14 @@
       <c r="K87" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L87" s="5" t="inlineStr">
-        <is>
-          <t>Высокий</t>
+      <c r="L87" s="7" t="inlineStr">
+        <is>
+          <t>Низкий</t>
         </is>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
-          <t>уровень ответственности (ОДО) не установлен</t>
+          <t>НОСТРОЙ действителен; дел по подряду 2025+ нет; штрафов нет</t>
         </is>
       </c>
     </row>
@@ -14066,7 +14066,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>не установлен</t>
+          <t>Первый уровень</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
@@ -14077,7 +14077,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>уровень ответственности (ОДО) не установлен; арбитражные дела по подряду 2025+ (1)</t>
+          <t>арбитражные дела по подряду 2025+ (1)</t>
         </is>
       </c>
     </row>
@@ -14659,12 +14659,12 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>СМУСпецМонтаж</t>
+          <t>АСМ-Инжиниринг</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>6102040797</t>
+          <t>6165187104</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -14674,7 +14674,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Первый уровень</t>
+          <t>Второй уровень</t>
         </is>
       </c>
       <c r="F50" s="3" t="n">
@@ -14697,12 +14697,12 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Строймонтаждон</t>
+          <t>СМУСпецМонтаж</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>6164138344</t>
+          <t>6102040797</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Недодаев Александр Сергеевич</t>
+          <t>Айрапетян Игнат Аршавирович</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>612401635847</t>
+          <t>615522305969</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -14773,12 +14773,12 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>СК СТРОЙИМПУЛЬС</t>
+          <t>Строймонтаждон</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>6164291494</t>
+          <t>6164138344</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -14788,7 +14788,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>не установлен</t>
+          <t>Первый уровень</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
@@ -14799,7 +14799,7 @@
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>статус НОСТРОЙ приостановлен; уровень ответственности (ОДО) не установлен</t>
+          <t>статус НОСТРОЙ приостановлен</t>
         </is>
       </c>
     </row>
@@ -14811,22 +14811,22 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Строй Альянс Юг</t>
+          <t>НОЙОН</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>6168058072</t>
+          <t>0816037238</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>действителен</t>
+          <t>приостановлен</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>не установлен</t>
+          <t>Первый уровень</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
@@ -14837,7 +14837,7 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>уровень ответственности (ОДО) не установлен</t>
+          <t>статус НОСТРОЙ приостановлен</t>
         </is>
       </c>
     </row>
@@ -14849,12 +14849,12 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>ДИКЕ</t>
+          <t>Недодаев Александр Сергеевич</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>6139004428</t>
+          <t>612401635847</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>не установлен</t>
+          <t>Первый уровень</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
@@ -14875,7 +14875,7 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>статус НОСТРОЙ приостановлен; уровень ответственности (ОДО) не установлен</t>
+          <t>статус НОСТРОЙ приостановлен</t>
         </is>
       </c>
     </row>
@@ -14887,17 +14887,17 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Клименков Максим Сергеевич</t>
+          <t>СК СТРОЙИМПУЛЬС</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>616610744501</t>
+          <t>6164291494</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>действителен</t>
+          <t>приостановлен</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -14913,7 +14913,7 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>уровень ответственности (ОДО) не установлен</t>
+          <t>статус НОСТРОЙ приостановлен; уровень ответственности (ОДО) не установлен</t>
         </is>
       </c>
     </row>
@@ -14925,22 +14925,22 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Мегаполис</t>
+          <t>ОООЮЖПРОМГЕОЛОГИЯ</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>6164280527</t>
+          <t>6155064061</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>действителен</t>
+          <t>приостановлен</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>не установлен</t>
+          <t>Первый уровень</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>уровень ответственности (ОДО) не установлен</t>
+          <t>статус НОСТРОЙ приостановлен</t>
         </is>
       </c>
     </row>
@@ -14963,109 +14963,109 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
+          <t>ДИКЕ</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>6139004428</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>приостановлен</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>не установлен</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>статус НОСТРОЙ приостановлен; уровень ответственности (ОДО) не установлен</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Клименков Максим Сергеевич</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>616610744501</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>действителен</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>не установлен</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>уровень ответственности (ОДО) не установлен</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
           <t>ИНСИТИ</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>6165175518</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>приостановлен</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>не установлен</t>
         </is>
       </c>
-      <c r="F58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
+      <c r="F60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
         <is>
           <t>статус НОСТРОЙ приостановлен; уровень ответственности (ОДО) не установлен</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>Средний</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>ДОММАСТЕР</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>0800019547</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>действителен</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>Первый уровень</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" s="4" t="n">
-        <v>765551.85</v>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>небольшие штрафы/неустойки 765 552 ₽</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>Средний</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>СК Сварог</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>6165150168</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>действителен</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>Второй уровень</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="4" t="n">
-        <v>303572.19</v>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>небольшие штрафы/неустойки 303 572 ₽</t>
         </is>
       </c>
     </row>
@@ -15077,109 +15077,109 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
+          <t>ДОММАСТЕР</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>0800019547</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>действителен</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Первый уровень</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>765551.85</v>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>небольшие штрафы/неустойки 765 552 ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>СК Сварог</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>6165150168</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>действителен</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Второй уровень</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>303572.19</v>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>небольшие штрафы/неустойки 303 572 ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
           <t>СК ГОРИЗОНТ</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>6141047940</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>действителен</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>Первый уровень</t>
         </is>
       </c>
-      <c r="F61" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" s="4" t="n">
+      <c r="F63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="4" t="n">
         <v>5000</v>
       </c>
-      <c r="H61" s="3" t="inlineStr">
+      <c r="H63" s="3" t="inlineStr">
         <is>
           <t>небольшие штрафы/неустойки 5 000 ₽</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>Монтаж плюс</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>6143075975</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>действителен</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>Первый уровень</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>НОСТРОЙ действителен; дел по подряду 2025+ нет; штрафов нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>Телефонстрой</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>6163143503</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>действителен</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>Первый уровень</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>НОСТРОЙ действителен; дел по подряду 2025+ нет; штрафов нет</t>
         </is>
       </c>
     </row>
@@ -15191,12 +15191,12 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>РусЮгСтрой</t>
+          <t>Монтаж плюс</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>6125029253</t>
+          <t>6143075975</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Второй уровень</t>
+          <t>Первый уровень</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>АРИАЛ</t>
+          <t>Телефонстрой</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>6166065317</t>
+          <t>6163143503</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -15244,7 +15244,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Второй уровень</t>
+          <t>Первый уровень</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
@@ -15267,12 +15267,12 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>СтройЭлектроМонтаж</t>
+          <t>РусЮгСтрой</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>6163126307</t>
+          <t>6125029253</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -15282,7 +15282,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Первый уровень</t>
+          <t>Второй уровень</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
@@ -15305,12 +15305,12 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>АСМ-Инжиниринг</t>
+          <t>АРИАЛ</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>6165187104</t>
+          <t>6166065317</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -15343,12 +15343,12 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Интеллектика</t>
+          <t>СтройЭлектроМонтаж</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>6166061471</t>
+          <t>6163126307</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -15381,12 +15381,12 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>ОООДонСтройПрогресс</t>
+          <t>Интеллектика</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>6165161931</t>
+          <t>6166061471</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -15419,12 +15419,12 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>ПСК</t>
+          <t>ОООДонСтройПрогресс</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>6143070582</t>
+          <t>6165161931</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -15457,12 +15457,12 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>НПП Вибробит</t>
+          <t>ПСК</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>6163009297</t>
+          <t>6143070582</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -15495,12 +15495,12 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>МДС</t>
+          <t>НПП Вибробит</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>6165167732</t>
+          <t>6163009297</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -15510,7 +15510,7 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Второй уровень</t>
+          <t>Первый уровень</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
@@ -15533,12 +15533,12 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>ИНЖЕНЕРНЫЕ РЕШЕНИЯ</t>
+          <t>МДС</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>6143096171</t>
+          <t>6165167732</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -15548,7 +15548,7 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Первый уровень</t>
+          <t>Второй уровень</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
@@ -15571,12 +15571,12 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Айрапетян Игнат Аршавирович</t>
+          <t>ИНЖЕНЕРНЫЕ РЕШЕНИЯ</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>615522305969</t>
+          <t>6143096171</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>НОЙОН</t>
+          <t>ИНКОМ</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>0816037238</t>
+          <t>0816030754</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Первый уровень</t>
+          <t>Второй уровень</t>
         </is>
       </c>
       <c r="F75" s="3" t="n">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>ИНКОМ</t>
+          <t>Альянс-Т</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>0816030754</t>
+          <t>6162074590</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -15685,12 +15685,12 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Альянс-Т</t>
+          <t>РемСтрой</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>6162074590</t>
+          <t>0816010067</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -15700,7 +15700,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Второй уровень</t>
+          <t>Первый уровень</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
@@ -15723,12 +15723,12 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>РемСтрой</t>
+          <t>Гаджиева Лала Гамид Кызы</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>0816010067</t>
+          <t>614909563219</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -15761,12 +15761,12 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>ОООЮЖПРОМГЕОЛОГИЯ</t>
+          <t>Гнатюк Юрий Степанович</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>6155064061</t>
+          <t>612802867122</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -15799,12 +15799,12 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Гаджиева Лала Гамид Кызы</t>
+          <t>Строй Альянс Юг</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>614909563219</t>
+          <t>6168058072</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Гнатюк Юрий Степанович</t>
+          <t>Кошаташян Амлет Грандович</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>612802867122</t>
+          <t>610200085371</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -15852,7 +15852,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Первый уровень</t>
+          <t>Второй уровень</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
@@ -15875,12 +15875,12 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Кошаташян Амлет Грандович</t>
+          <t>Патриот</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>610200085371</t>
+          <t>0816027053</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -15890,7 +15890,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Второй уровень</t>
+          <t>Первый уровень</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
@@ -15913,12 +15913,12 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Патриот</t>
+          <t>НИКА</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>0816027053</t>
+          <t>0816034124</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -15928,7 +15928,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Первый уровень</t>
+          <t>Второй уровень</t>
         </is>
       </c>
       <c r="F83" s="3" t="n">
@@ -15951,12 +15951,12 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>НИКА</t>
+          <t>ДВР</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>0816034124</t>
+          <t>6163207475</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Второй уровень</t>
+          <t>Третий уровень</t>
         </is>
       </c>
       <c r="F84" s="3" t="n">
@@ -15989,12 +15989,12 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>ДВР</t>
+          <t>ЭЛЕМЕНТ СИТИ СТРОЙ</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>6163207475</t>
+          <t>6143099278</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -16004,7 +16004,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Третий уровень</t>
+          <t>Второй уровень</t>
         </is>
       </c>
       <c r="F85" s="3" t="n">
@@ -16027,12 +16027,12 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>ЭЛЕМЕНТ СИТИ СТРОЙ</t>
+          <t>ТАМАРА</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>6143099278</t>
+          <t>6166129874</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -16042,7 +16042,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>Второй уровень</t>
+          <t>Первый уровень</t>
         </is>
       </c>
       <c r="F86" s="3" t="n">
@@ -16065,12 +16065,12 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>ТАМАРА</t>
+          <t>САНРАЙЗ-СТРОЙ</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>6166129874</t>
+          <t>0800015937</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -16080,7 +16080,7 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Первый уровень</t>
+          <t>Второй уровень</t>
         </is>
       </c>
       <c r="F87" s="3" t="n">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>САНРАЙЗ-СТРОЙ</t>
+          <t>Цыбанев Игорь Николаевич</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>0800015937</t>
+          <t>080500824511</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -16118,7 +16118,7 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>Второй уровень</t>
+          <t>Первый уровень</t>
         </is>
       </c>
       <c r="F88" s="3" t="n">
@@ -16141,12 +16141,12 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Цыбанев Игорь Николаевич</t>
+          <t>Мегаполис</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>080500824511</t>
+          <t>6164280527</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
